--- a/ttl_long/AdHoc_Net_6.xlsx
+++ b/ttl_long/AdHoc_Net_6.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>91</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>299</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>52</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>203</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>78</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>94</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>262</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>212</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>422</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>351</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>283</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>86</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>423</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>180</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>467</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>93</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>607</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>99</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>401</t>
+          <t>597</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>601</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>709</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>721</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>795</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>925</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>260</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>896</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>996</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>1119</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>205</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>1059</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>1150</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>77</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1225</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>1173</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>1220</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>79</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1359</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>136</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1434</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>279</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>1397</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>460</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>271</t>
         </is>
       </c>
     </row>
@@ -970,318 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>346</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>984</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>991</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1190</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1133</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1253</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1255</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1308</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1438</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1465</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1531</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1536</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1613</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1615</t>
+          <t>1273</t>
         </is>
       </c>
     </row>
@@ -1296,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,7 +1023,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1351,7 +1045,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1373,7 +1067,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1395,7 +1089,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1417,7 +1111,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1439,7 +1133,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1461,7 +1155,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1478,12 +1172,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,7 +1199,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1527,7 +1221,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1549,7 +1243,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1571,7 +1265,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1593,7 +1287,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1632,12 +1326,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1654,12 +1348,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1681,7 +1375,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1703,7 +1397,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1725,7 +1419,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1747,7 +1441,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1764,12 +1458,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1791,7 +1485,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1813,7 +1507,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1835,7 +1529,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1852,12 +1546,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1879,7 +1573,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1896,12 +1590,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1918,12 +1612,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1940,12 +1634,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1962,12 +1656,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1984,12 +1678,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2006,12 +1700,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2028,12 +1722,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2050,12 +1744,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2072,12 +1766,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2094,12 +1788,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2116,12 +1810,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2138,12 +1832,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2160,12 +1854,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2182,12 +1876,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2204,12 +1898,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2226,7 +1920,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2248,12 +1942,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2270,12 +1964,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2292,12 +1986,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2314,12 +2008,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2336,12 +2030,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2358,7 +2052,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2380,12 +2074,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2402,12 +2096,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2424,12 +2118,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2446,12 +2140,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2468,12 +2162,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2490,12 +2184,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2512,12 +2206,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2534,12 +2228,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2556,12 +2250,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2578,7 +2272,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2600,12 +2294,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2622,12 +2316,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2644,12 +2338,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2666,12 +2360,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2688,12 +2382,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2710,12 +2404,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2732,12 +2426,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2754,12 +2448,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2776,12 +2470,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2798,12 +2492,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2820,12 +2514,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2842,12 +2536,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2864,12 +2558,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2886,12 +2580,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2908,12 +2602,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2930,12 +2624,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2952,12 +2646,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2974,12 +2668,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2996,12 +2690,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3018,12 +2712,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3032,1678 +2726,6 @@
         </is>
       </c>
       <c r="D79" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -4752,7 +2774,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -4778,7 +2800,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jamm_powe</t>
+          <t>jamm_power</t>
         </is>
       </c>
       <c r="B6" t="n">

--- a/ttl_long/AdHoc_Net_6.xlsx
+++ b/ttl_long/AdHoc_Net_6.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>183</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>312</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>194</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>298</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>280</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>170</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>336</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>277</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>414</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>448</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>326</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>410</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>526</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>253</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>499</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>72</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>636</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>607</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>310</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>795</t>
+          <t>659</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>829</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>173</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>685</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>779</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>242</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>851</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>888</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>1041</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>230</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1033</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>956</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1160</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>130</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1105</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>314</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1128</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>1242</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,165 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>168</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1156</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1508</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1661</t>
         </is>
       </c>
     </row>
@@ -990,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1023,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1045,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1067,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1089,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1133,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1155,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1172,12 +1325,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1199,7 +1352,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1221,7 +1374,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1243,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1287,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1309,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1326,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1353,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1370,12 +1523,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1397,7 +1550,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1414,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1436,12 +1589,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1458,12 +1611,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1480,7 +1633,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1502,7 +1655,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1551,7 +1704,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1590,12 +1743,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1639,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1661,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1678,12 +1831,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1700,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1727,7 +1880,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1744,12 +1897,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1771,7 +1924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1788,12 +1941,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1810,12 +1963,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1832,12 +1985,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1854,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1876,12 +2029,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1898,12 +2051,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1920,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1942,12 +2095,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1964,12 +2117,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1986,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2008,12 +2161,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2030,12 +2183,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2052,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2074,12 +2227,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2096,12 +2249,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2118,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2140,12 +2293,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2162,12 +2315,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2184,12 +2337,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2206,12 +2359,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2228,12 +2381,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2250,12 +2403,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2272,12 +2425,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2294,12 +2447,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2316,12 +2469,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2338,12 +2491,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2360,12 +2513,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2382,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2404,12 +2557,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2426,12 +2579,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2448,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2470,12 +2623,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2492,12 +2645,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2514,12 +2667,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2536,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2558,12 +2711,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2580,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2602,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2624,12 +2777,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2646,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2668,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2690,12 +2843,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2712,20 +2865,878 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -2774,7 +3785,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -2794,7 +3805,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">

--- a/ttl_long/AdHoc_Net_6.xlsx
+++ b/ttl_long/AdHoc_Net_6.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -460,12 +460,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
     </row>
@@ -477,12 +477,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>89</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>194</t>
         </is>
       </c>
     </row>
@@ -511,12 +511,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>270</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>62</t>
         </is>
       </c>
     </row>
@@ -528,12 +528,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>308</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>107</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>253</t>
         </is>
       </c>
     </row>
@@ -562,12 +562,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>198</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>310</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>307</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>277</t>
+          <t>235</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>448</t>
         </is>
       </c>
     </row>
@@ -613,12 +613,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>147</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>309</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>362</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>460</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>216</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>565</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>323</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>507</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>582</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>698</t>
         </is>
       </c>
     </row>
@@ -732,12 +732,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>275</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>643</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>821</t>
         </is>
       </c>
     </row>
@@ -766,12 +766,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>773</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>747</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>955</t>
         </is>
       </c>
     </row>
@@ -817,12 +817,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>158</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>849</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>829</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>47</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>984</t>
         </is>
       </c>
     </row>
@@ -868,12 +868,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>146</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>993</t>
         </is>
       </c>
     </row>
@@ -885,12 +885,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>341</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1015</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1149</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>197</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1084</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1091</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>107</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1242</t>
+          <t>1227</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>88</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1288</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1260</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>73</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1431</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>142</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1400</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>281</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1330</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1533</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>237</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1412</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1454</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1603</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>153</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1591</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1479,12 +1479,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1545,7 +1545,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1567,12 +1567,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,12 +1699,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1853,12 +1853,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1919,12 +1919,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2073,12 +2073,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2139,12 +2139,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2271,12 +2271,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2535,12 +2535,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2667,7 +2667,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2689,12 +2689,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2755,12 +2755,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2887,12 +2887,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3019,12 +3019,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,12 +3041,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3085,12 +3085,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>29</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3129,12 +3129,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,12 +3173,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3195,12 +3195,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3261,12 +3261,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3415,12 +3415,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3525,12 +3525,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3657,12 +3657,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3679,12 +3679,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3728,15 +3728,81 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
         <is>
           <t>3000</t>
         </is>
@@ -3775,7 +3841,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
